--- a/static/data/exports/Retro_UK_AE_2022.xlsx
+++ b/static/data/exports/Retro_UK_AE_2022.xlsx
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -52121,20 +52121,20 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>1491985</v>
+        <v>1491986</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Asif Miyan</t>
+          <t>Vijay Pal</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>AIMIM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D702" t="n">
-        <v>16145</v>
+        <v>16079</v>
       </c>
       <c r="E702" t="n">
         <v>80</v>
@@ -52158,12 +52158,12 @@
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>Asif Miyan</t>
+          <t>Vijay Pal</t>
         </is>
       </c>
       <c r="L702" t="inlineStr">
         <is>
-          <t>AIMIM</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="N702" t="inlineStr">
@@ -52177,7 +52177,7 @@
         </is>
       </c>
       <c r="P702" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q702" t="b">
         <v>0</v>
@@ -52196,20 +52196,20 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>1491986</v>
+        <v>1491985</v>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Vijay Pal</t>
+          <t>Asif Miyan</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AIMIM</t>
         </is>
       </c>
       <c r="D703" t="n">
-        <v>16079</v>
+        <v>16145</v>
       </c>
       <c r="E703" t="n">
         <v>80</v>
@@ -52233,12 +52233,12 @@
       </c>
       <c r="K703" t="inlineStr">
         <is>
-          <t>Vijay Pal</t>
+          <t>Asif Miyan</t>
         </is>
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>AIMIM</t>
         </is>
       </c>
       <c r="N703" t="inlineStr">
@@ -52252,7 +52252,7 @@
         </is>
       </c>
       <c r="P703" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q703" t="b">
         <v>0</v>
